--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_mobile_product_card.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/device/primary_device_vs_mobile_product_card.xlsx
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>15</v>
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
